--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,14 +841,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45163.60819018595</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -900,16 +896,6 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -965,10 +951,9 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>450.425</v>
-      </c>
-    </row>
-    <row r="30"/>
+        <v>517.989</v>
+      </c>
+    </row>
     <row r="31" ht="15.75" customHeight="1" s="17">
       <c r="B31" s="27" t="inlineStr">
         <is>
@@ -977,9 +962,6 @@
       </c>
       <c r="D31" s="44" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -999,33 +981,29 @@
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="B39" s="34" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -992,18 +992,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -992,18 +992,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,7 +841,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,10 +841,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45267</v>
+        <v>45261.57767636236</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -896,6 +900,16 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -951,9 +965,10 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>517.989</v>
-      </c>
-    </row>
+        <v>792.86</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31" ht="15.75" customHeight="1" s="17">
       <c r="B31" s="27" t="inlineStr">
         <is>
@@ -962,6 +977,9 @@
       </c>
       <c r="D31" s="44" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -981,29 +999,33 @@
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="B39" s="34" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRA ARTICULADA.xlsx
+++ b/LISTAS/mi/BISAGRA ARTICULADA.xlsx
@@ -841,14 +841,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45261.57767636236</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -900,16 +896,6 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -965,10 +951,9 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>792.86</v>
-      </c>
-    </row>
-    <row r="30"/>
+        <v>517.989</v>
+      </c>
+    </row>
     <row r="31" ht="15.75" customHeight="1" s="17">
       <c r="B31" s="27" t="inlineStr">
         <is>
@@ -977,9 +962,6 @@
       </c>
       <c r="D31" s="44" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -999,33 +981,29 @@
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="B39" s="34" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
